--- a/backend/data/financials_by_company/1D3.SI.xlsx
+++ b/backend/data/financials_by_company/1D3.SI.xlsx
@@ -3740,10 +3740,8 @@
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>068877</t>
-        </is>
+      <c r="D2" t="n">
+        <v>68877</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3960,7 +3958,7 @@
         <v>-1618000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
         <v>11.22</v>
